--- a/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:24</t>
+    <t xml:space="preserve">2026-09-09 21:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:13</t>
+    <t xml:space="preserve">2026-09-18 12:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
@@ -6,58 +6,99 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Serie" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Nivel" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tramos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Serie'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tramos'!$A$1:$B$4</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t xml:space="preserve">Grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujeres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 15:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plot_nacional_serie_e_rezmat_a_2021.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E_REZMAT_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile (Nacional)</t>
+  </si>
   <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de creación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18 12:02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIT - MDSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagen asociada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plot_nacional_serie_e_rezmat_a_2021.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rezago respecto de la población matriculada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad territorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chile (Nacional)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivel educativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Básica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media humanista-científica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media técnico-profesional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramo de edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 a 13 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 a 17 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 a 21 años</t>
   </si>
 </sst>
 </file>
@@ -423,7 +464,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -435,63 +476,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>2018</v>
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2019</v>
+      <c r="A3" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.19</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>2020</v>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -508,62 +517,158 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="28.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>53.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 15:14</t>
+    <t xml:space="preserve">2026-10-01 16:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 16:35</t>
+    <t xml:space="preserve">2026-10-01 19:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
@@ -10,15 +10,17 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Nivel" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tramos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Serie_total" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Serie_sexo" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tramos'!$A$1:$B$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Serie_sexo'!$A$1:$C$8</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">Grupo</t>
   </si>
@@ -44,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:22</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -99,6 +101,15 @@
   </si>
   <si>
     <t xml:space="preserve">18 a 21 años</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezago (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujeres (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hombres (%)</t>
   </si>
 </sst>
 </file>
@@ -671,4 +682,189 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="13.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_e_rezmat_a_2021.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 06:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
